--- a/data/trans_camb/P34A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,95; -16,99</t>
+          <t>-26,83; -16,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -3,81</t>
+          <t>-14,48; -4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -0,56</t>
+          <t>-11,88; -0,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,56; -9,28</t>
+          <t>-19,72; -9,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 9,64</t>
+          <t>-1,1; 9,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 1,52</t>
+          <t>-7,89; 1,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,47; -14,4</t>
+          <t>-21,62; -14,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 1,4</t>
+          <t>-6,38; 1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -0,97</t>
+          <t>-8,36; -0,93</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,93; -39,87</t>
+          <t>-56,32; -39,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,38; -8,34</t>
+          <t>-30,99; -10,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,86; -1,26</t>
+          <t>-25,38; -1,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -23,85</t>
+          <t>-44,24; -23,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 24,68</t>
+          <t>-2,82; 25,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 3,81</t>
+          <t>-17,66; 4,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,14; -34,98</t>
+          <t>-48,3; -34,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 3,53</t>
+          <t>-13,92; 3,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -2,27</t>
+          <t>-18,6; -2,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,28; -13,47</t>
+          <t>-22,89; -13,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -2,18</t>
+          <t>-11,5; -2,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,53; -7,43</t>
+          <t>-29,71; -7,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -6,55</t>
+          <t>-15,56; -6,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 0,34</t>
+          <t>-8,84; 0,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -4,37</t>
+          <t>-12,86; -4,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,72; -11,33</t>
+          <t>-17,35; -11,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -2,45</t>
+          <t>-8,57; -2,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,1; -7,89</t>
+          <t>-24,78; -7,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,13; -33,53</t>
+          <t>-51,15; -34,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,33; -5,35</t>
+          <t>-26,45; -6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,08; -17,58</t>
+          <t>-67,38; -17,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,9; -14,51</t>
+          <t>-31,47; -14,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 0,84</t>
+          <t>-18,01; 0,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,87; -9,7</t>
+          <t>-26,1; -10,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,14; -26,29</t>
+          <t>-37,88; -26,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,34; -5,69</t>
+          <t>-18,66; -5,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,17; -17,78</t>
+          <t>-54,71; -17,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -7,14</t>
+          <t>-16,72; -7,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 5,53</t>
+          <t>-4,75; 5,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 7,12</t>
+          <t>-3,95; 6,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -6,28</t>
+          <t>-15,79; -5,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,09</t>
+          <t>-4,16; 6,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 11,11</t>
+          <t>-21,65; 10,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,81; -7,59</t>
+          <t>-14,84; -8,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,93</t>
+          <t>-2,99; 4,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 6,86</t>
+          <t>-12,14; 7,14</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,52; -23,9</t>
+          <t>-47,63; -23,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 18,69</t>
+          <t>-13,64; 16,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 23,8</t>
+          <t>-11,14; 22,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,55; -17,31</t>
+          <t>-38,04; -14,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 16,61</t>
+          <t>-9,88; 17,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 29,47</t>
+          <t>-52,33; 28,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,37; -22,52</t>
+          <t>-39,26; -23,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 11,47</t>
+          <t>-7,97; 12,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 19,31</t>
+          <t>-32,97; 20,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,57; -17,5</t>
+          <t>-25,57; -16,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -7,19</t>
+          <t>-15,28; -6,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -9,9</t>
+          <t>-18,66; -9,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,74; -17,98</t>
+          <t>-27,26; -18,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -5,77</t>
+          <t>-14,53; -5,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,17; -10,52</t>
+          <t>-22,33; -10,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,04; -19,18</t>
+          <t>-25,18; -19,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -7,25</t>
+          <t>-14,12; -7,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,13; -10,96</t>
+          <t>-18,33; -11,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,0; -42,45</t>
+          <t>-56,57; -41,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,29; -17,11</t>
+          <t>-33,85; -15,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; -23,71</t>
+          <t>-40,84; -23,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,01; -35,75</t>
+          <t>-49,43; -36,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,62; -11,51</t>
+          <t>-26,49; -11,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -20,66</t>
+          <t>-41,17; -19,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,34; -40,53</t>
+          <t>-50,63; -41,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,23; -15,46</t>
+          <t>-28,49; -16,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,42; -23,41</t>
+          <t>-36,97; -23,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -16,22</t>
+          <t>-20,83; -16,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -4,69</t>
+          <t>-9,75; -4,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -6,9</t>
+          <t>-16,72; -6,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -12,67</t>
+          <t>-17,48; -12,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -1,31</t>
+          <t>-5,77; -0,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -4,63</t>
+          <t>-16,25; -4,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -15,23</t>
+          <t>-18,44; -15,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -3,61</t>
+          <t>-6,95; -3,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -6,28</t>
+          <t>-13,38; -6,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -40,56</t>
+          <t>-49,52; -41,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -11,68</t>
+          <t>-22,99; -11,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -16,96</t>
+          <t>-40,87; -17,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -28,18</t>
+          <t>-36,99; -28,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -2,98</t>
+          <t>-12,33; -2,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -10,28</t>
+          <t>-34,22; -10,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,64; -35,53</t>
+          <t>-41,52; -35,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -8,55</t>
+          <t>-15,55; -8,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -14,41</t>
+          <t>-30,65; -14,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P34A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,11</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,71</t>
+          <t>-4,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,83; -16,84</t>
+          <t>-26,87; -16,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -4,29</t>
+          <t>-14,85; -3,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -0,5</t>
+          <t>-11,24; 0,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,72; -9,33</t>
+          <t>-19,6; -9,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,76</t>
+          <t>-0,89; 10,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,78</t>
+          <t>-7,98; 2,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,62; -14,2</t>
+          <t>-21,23; -14,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,39</t>
+          <t>-6,63; 1,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -0,93</t>
+          <t>-7,94; -0,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-14,03%</t>
+          <t>-12,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,5%</t>
+          <t>-6,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,91%</t>
+          <t>-9,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,32; -39,08</t>
+          <t>-56,07; -38,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -10,32</t>
+          <t>-31,3; -9,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,38; -1,19</t>
+          <t>-23,88; 0,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,24; -23,89</t>
+          <t>-44,29; -24,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 25,36</t>
+          <t>-2,1; 26,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 4,58</t>
+          <t>-17,79; 5,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,3; -34,93</t>
+          <t>-47,73; -35,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 3,41</t>
+          <t>-14,59; 3,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,6; -2,34</t>
+          <t>-17,32; -1,9</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-15,77</t>
+          <t>-8,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,72</t>
+          <t>-8,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-12,91</t>
+          <t>-8,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -13,77</t>
+          <t>-22,16; -13,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -2,47</t>
+          <t>-11,38; -2,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,71; -7,23</t>
+          <t>-13,27; -4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -6,73</t>
+          <t>-15,87; -6,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 0,19</t>
+          <t>-9,23; 0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,86; -4,56</t>
+          <t>-12,96; -4,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -11,17</t>
+          <t>-17,54; -11,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; -2,53</t>
+          <t>-8,85; -1,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -7,6</t>
+          <t>-12,14; -5,95</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-37,44%</t>
+          <t>-21,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-18,47%</t>
+          <t>-18,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,9%</t>
+          <t>-19,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,15; -34,55</t>
+          <t>-50,14; -34,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -6,6</t>
+          <t>-25,09; -4,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,38; -17,71</t>
+          <t>-29,96; -10,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,47; -14,72</t>
+          <t>-32,26; -14,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 0,42</t>
+          <t>-18,29; 0,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,1; -10,11</t>
+          <t>-26,28; -10,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,88; -26,32</t>
+          <t>-37,79; -25,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -5,95</t>
+          <t>-19,03; -4,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,71; -17,47</t>
+          <t>-25,96; -13,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>5,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -7,38</t>
+          <t>-16,78; -7,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 5,05</t>
+          <t>-4,51; 5,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 6,83</t>
+          <t>-3,09; 7,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -5,43</t>
+          <t>-16,03; -5,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 6,29</t>
+          <t>-4,89; 5,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 10,99</t>
+          <t>0,56; 10,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -8,09</t>
+          <t>-14,63; -8,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,34</t>
+          <t>-2,98; 4,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 7,14</t>
+          <t>0,56; 7,68</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,38%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,63; -23,54</t>
+          <t>-47,1; -24,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 16,73</t>
+          <t>-12,77; 18,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 22,51</t>
+          <t>-8,55; 25,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,04; -14,94</t>
+          <t>-38,03; -15,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 17,6</t>
+          <t>-11,63; 15,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 28,5</t>
+          <t>1,27; 29,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,26; -23,54</t>
+          <t>-38,87; -23,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 12,7</t>
+          <t>-7,97; 11,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 20,31</t>
+          <t>1,29; 22,36</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-14,16</t>
+          <t>-14,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,19</t>
+          <t>-12,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,52</t>
+          <t>-13,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,57; -16,93</t>
+          <t>-25,65; -17,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -6,45</t>
+          <t>-15,86; -7,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -9,97</t>
+          <t>-19,05; -10,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,26; -18,7</t>
+          <t>-26,64; -18,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -5,66</t>
+          <t>-14,88; -5,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,33; -10,08</t>
+          <t>-16,56; -8,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,18; -19,34</t>
+          <t>-25,04; -19,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -7,82</t>
+          <t>-13,95; -7,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -11,28</t>
+          <t>-16,54; -10,6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-34,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,66%</t>
+          <t>-23,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,04%</t>
+          <t>-27,89%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,57; -41,17</t>
+          <t>-56,53; -41,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,85; -15,98</t>
+          <t>-34,66; -17,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,84; -23,94</t>
+          <t>-41,99; -25,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,43; -36,79</t>
+          <t>-48,58; -35,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -11,06</t>
+          <t>-27,14; -11,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,17; -19,81</t>
+          <t>-29,84; -16,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,63; -41,22</t>
+          <t>-50,3; -40,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -16,57</t>
+          <t>-27,83; -16,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,97; -23,81</t>
+          <t>-33,36; -23,03</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-7,62</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>-6,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -16,49</t>
+          <t>-20,84; -16,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -4,63</t>
+          <t>-9,63; -4,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -6,86</t>
+          <t>-10,28; -5,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -12,8</t>
+          <t>-17,47; -12,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -0,92</t>
+          <t>-5,72; -0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -4,61</t>
+          <t>-7,93; -3,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -15,26</t>
+          <t>-18,42; -15,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -3,56</t>
+          <t>-7,07; -3,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -6,49</t>
+          <t>-8,16; -4,88</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-18,55%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-17,7%</t>
+          <t>-12,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-20,86%</t>
+          <t>-15,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,52; -41,25</t>
+          <t>-49,31; -40,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,99; -11,44</t>
+          <t>-22,76; -12,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,87; -17,1</t>
+          <t>-24,19; -12,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,99; -28,46</t>
+          <t>-37,11; -28,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,07</t>
+          <t>-12,07; -1,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -10,1</t>
+          <t>-16,65; -7,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -35,45</t>
+          <t>-41,4; -35,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -8,29</t>
+          <t>-15,82; -8,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -14,9</t>
+          <t>-18,36; -11,49</t>
         </is>
       </c>
     </row>
